--- a/data/input/상장폐지현황.xlsx
+++ b/data/input/상장폐지현황.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kwoss_C\kwoss-data-collection\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{492511E5-F3E3-4487-8AFF-336840306774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF1AB6C-65E5-4792-A7C5-6051AEB9292C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10310" yWindow="5430" windowWidth="22970" windowHeight="15370" xr2:uid="{8BCDFC86-22AF-4EBB-88AB-B71FC58BBAF8}"/>
+    <workbookView xWindow="1370" yWindow="5080" windowWidth="22970" windowHeight="15370" xr2:uid="{8BCDFC86-22AF-4EBB-88AB-B71FC58BBAF8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="779">
   <si>
     <t>종목코드</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,13 +52,2338 @@
   <si>
     <t>폐지사유</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>204650</t>
+  </si>
+  <si>
+    <t>204760</t>
+  </si>
+  <si>
+    <t>035720</t>
+  </si>
+  <si>
+    <t>204440</t>
+  </si>
+  <si>
+    <t>036500</t>
+  </si>
+  <si>
+    <t>052270</t>
+  </si>
+  <si>
+    <t>086830</t>
+  </si>
+  <si>
+    <t>456490</t>
+  </si>
+  <si>
+    <t>052670</t>
+  </si>
+  <si>
+    <t>207930</t>
+  </si>
+  <si>
+    <t>226360</t>
+  </si>
+  <si>
+    <t>454640</t>
+  </si>
+  <si>
+    <t>455250</t>
+  </si>
+  <si>
+    <t>111870</t>
+  </si>
+  <si>
+    <t>208340</t>
+  </si>
+  <si>
+    <t>450050</t>
+  </si>
+  <si>
+    <t>150840</t>
+  </si>
+  <si>
+    <t>057880</t>
+  </si>
+  <si>
+    <t>054630</t>
+  </si>
+  <si>
+    <t>335890</t>
+  </si>
+  <si>
+    <t>215580</t>
+  </si>
+  <si>
+    <t>174880</t>
+  </si>
+  <si>
+    <t>448760</t>
+  </si>
+  <si>
+    <t>151910</t>
+  </si>
+  <si>
+    <t>446150</t>
+  </si>
+  <si>
+    <t>448830</t>
+  </si>
+  <si>
+    <t>478780</t>
+  </si>
+  <si>
+    <t>442770</t>
+  </si>
+  <si>
+    <t>449020</t>
+  </si>
+  <si>
+    <t>430220</t>
+  </si>
+  <si>
+    <t>446750</t>
+  </si>
+  <si>
+    <t>448370</t>
+  </si>
+  <si>
+    <t>442900</t>
+  </si>
+  <si>
+    <t>448740</t>
+  </si>
+  <si>
+    <t>096040</t>
+  </si>
+  <si>
+    <t>446190</t>
+  </si>
+  <si>
+    <t>290380</t>
+  </si>
+  <si>
+    <t>024810</t>
+  </si>
+  <si>
+    <t>445970</t>
+  </si>
+  <si>
+    <t>454750</t>
+  </si>
+  <si>
+    <t>019590</t>
+  </si>
+  <si>
+    <t>445360</t>
+  </si>
+  <si>
+    <t>044060</t>
+  </si>
+  <si>
+    <t>014200</t>
+  </si>
+  <si>
+    <t>438580</t>
+  </si>
+  <si>
+    <t>439730</t>
+  </si>
+  <si>
+    <t>442310</t>
+  </si>
+  <si>
+    <t>439410</t>
+  </si>
+  <si>
+    <t>226440</t>
+  </si>
+  <si>
+    <t>439250</t>
+  </si>
+  <si>
+    <t>437780</t>
+  </si>
+  <si>
+    <t>207720</t>
+  </si>
+  <si>
+    <t>023460</t>
+  </si>
+  <si>
+    <t>440820</t>
+  </si>
+  <si>
+    <t>440790</t>
+  </si>
+  <si>
+    <t>476470</t>
+  </si>
+  <si>
+    <t>950110</t>
+  </si>
+  <si>
+    <t>442130</t>
+  </si>
+  <si>
+    <t>071460</t>
+  </si>
+  <si>
+    <t>072520</t>
+  </si>
+  <si>
+    <t>323230</t>
+  </si>
+  <si>
+    <t>029960</t>
+  </si>
+  <si>
+    <t>468510</t>
+  </si>
+  <si>
+    <t>477530</t>
+  </si>
+  <si>
+    <t>457390</t>
+  </si>
+  <si>
+    <t>433530</t>
+  </si>
+  <si>
+    <t>078940</t>
+  </si>
+  <si>
+    <t>268600</t>
+  </si>
+  <si>
+    <t>413600</t>
+  </si>
+  <si>
+    <t>435380</t>
+  </si>
+  <si>
+    <t>160600</t>
+  </si>
+  <si>
+    <t>299910</t>
+  </si>
+  <si>
+    <t>376190</t>
+  </si>
+  <si>
+    <t>435620</t>
+  </si>
+  <si>
+    <t>214870</t>
+  </si>
+  <si>
+    <t>435870</t>
+  </si>
+  <si>
+    <t>418210</t>
+  </si>
+  <si>
+    <t>456440</t>
+  </si>
+  <si>
+    <t>458320</t>
+  </si>
+  <si>
+    <t>038340</t>
+  </si>
+  <si>
+    <t>430700</t>
+  </si>
+  <si>
+    <t>263540</t>
+  </si>
+  <si>
+    <t>425290</t>
+  </si>
+  <si>
+    <t>080000</t>
+  </si>
+  <si>
+    <t>415580</t>
+  </si>
+  <si>
+    <t>438220</t>
+  </si>
+  <si>
+    <t>164060</t>
+  </si>
+  <si>
+    <t>217810</t>
+  </si>
+  <si>
+    <t>214310</t>
+  </si>
+  <si>
+    <t>900280</t>
+  </si>
+  <si>
+    <t>418170</t>
+  </si>
+  <si>
+    <t>422040</t>
+  </si>
+  <si>
+    <t>424140</t>
+  </si>
+  <si>
+    <t>430460</t>
+  </si>
+  <si>
+    <t>421800</t>
+  </si>
+  <si>
+    <t>406760</t>
+  </si>
+  <si>
+    <t>138580</t>
+  </si>
+  <si>
+    <t>062860</t>
+  </si>
+  <si>
+    <t>412930</t>
+  </si>
+  <si>
+    <t>287410</t>
+  </si>
+  <si>
+    <t>119860</t>
+  </si>
+  <si>
+    <t>136510</t>
+  </si>
+  <si>
+    <t>053590</t>
+  </si>
+  <si>
+    <t>388800</t>
+  </si>
+  <si>
+    <t>089530</t>
+  </si>
+  <si>
+    <t>181340</t>
+  </si>
+  <si>
+    <t>065560</t>
+  </si>
+  <si>
+    <t>058530</t>
+  </si>
+  <si>
+    <t>900130</t>
+  </si>
+  <si>
+    <t>430230</t>
+  </si>
+  <si>
+    <t>400840</t>
+  </si>
+  <si>
+    <t>034230</t>
+  </si>
+  <si>
+    <t>006580</t>
+  </si>
+  <si>
+    <t>436610</t>
+  </si>
+  <si>
+    <t>058220</t>
+  </si>
+  <si>
+    <t>397880</t>
+  </si>
+  <si>
+    <t>115960</t>
+  </si>
+  <si>
+    <t>372290</t>
+  </si>
+  <si>
+    <t>393360</t>
+  </si>
+  <si>
+    <t>148140</t>
+  </si>
+  <si>
+    <t>386580</t>
+  </si>
+  <si>
+    <t>436530</t>
+  </si>
+  <si>
+    <t>419270</t>
+  </si>
+  <si>
+    <t>426550</t>
+  </si>
+  <si>
+    <t>427950</t>
+  </si>
+  <si>
+    <t>114120</t>
+  </si>
+  <si>
+    <t>066970</t>
+  </si>
+  <si>
+    <t>377400</t>
+  </si>
+  <si>
+    <t>380320</t>
+  </si>
+  <si>
+    <t>161570</t>
+  </si>
+  <si>
+    <t>405640</t>
+  </si>
+  <si>
+    <t>391060</t>
+  </si>
+  <si>
+    <t>091990</t>
+  </si>
+  <si>
+    <t>046140</t>
+  </si>
+  <si>
+    <t>377630</t>
+  </si>
+  <si>
+    <t>440200</t>
+  </si>
+  <si>
+    <t>085370</t>
+  </si>
+  <si>
+    <t>353060</t>
+  </si>
+  <si>
+    <t>138690</t>
+  </si>
+  <si>
+    <t>450410</t>
+  </si>
+  <si>
+    <t>373340</t>
+  </si>
+  <si>
+    <t>141020</t>
+  </si>
+  <si>
+    <t>069110</t>
+  </si>
+  <si>
+    <t>404950</t>
+  </si>
+  <si>
+    <t>366330</t>
+  </si>
+  <si>
+    <t>405350</t>
+  </si>
+  <si>
+    <t>367360</t>
+  </si>
+  <si>
+    <t>367480</t>
+  </si>
+  <si>
+    <t>022100</t>
+  </si>
+  <si>
+    <t>400560</t>
+  </si>
+  <si>
+    <t>100090</t>
+  </si>
+  <si>
+    <t>058420</t>
+  </si>
+  <si>
+    <t>056000</t>
+  </si>
+  <si>
+    <t>387310</t>
+  </si>
+  <si>
+    <t>426670</t>
+  </si>
+  <si>
+    <t>048260</t>
+  </si>
+  <si>
+    <t>050540</t>
+  </si>
+  <si>
+    <t>353070</t>
+  </si>
+  <si>
+    <t>023430</t>
+  </si>
+  <si>
+    <t>096640</t>
+  </si>
+  <si>
+    <t>367340</t>
+  </si>
+  <si>
+    <t>030190</t>
+  </si>
+  <si>
+    <t>298870</t>
+  </si>
+  <si>
+    <t>388220</t>
+  </si>
+  <si>
+    <t>090460</t>
+  </si>
+  <si>
+    <t>353490</t>
+  </si>
+  <si>
+    <t>396770</t>
+  </si>
+  <si>
+    <t>409570</t>
+  </si>
+  <si>
+    <t>078650</t>
+  </si>
+  <si>
+    <t>341160</t>
+  </si>
+  <si>
+    <t>367460</t>
+  </si>
+  <si>
+    <t>347140</t>
+  </si>
+  <si>
+    <t>126870</t>
+  </si>
+  <si>
+    <t>064510</t>
+  </si>
+  <si>
+    <t>337450</t>
+  </si>
+  <si>
+    <t>351340</t>
+  </si>
+  <si>
+    <t>206660</t>
+  </si>
+  <si>
+    <t>343510</t>
+  </si>
+  <si>
+    <t>108320</t>
+  </si>
+  <si>
+    <t>344050</t>
+  </si>
+  <si>
+    <t>158310</t>
+  </si>
+  <si>
+    <t>290510</t>
+  </si>
+  <si>
+    <t>131390</t>
+  </si>
+  <si>
+    <t>060300</t>
+  </si>
+  <si>
+    <t>349720</t>
+  </si>
+  <si>
+    <t>217600</t>
+  </si>
+  <si>
+    <t>342550</t>
+  </si>
+  <si>
+    <t>397500</t>
+  </si>
+  <si>
+    <t>950180</t>
+  </si>
+  <si>
+    <t>090740</t>
+  </si>
+  <si>
+    <t>176440</t>
+  </si>
+  <si>
+    <t>127160</t>
+  </si>
+  <si>
+    <t>340350</t>
+  </si>
+  <si>
+    <t>220630</t>
+  </si>
+  <si>
+    <t>330990</t>
+  </si>
+  <si>
+    <t>053660</t>
+  </si>
+  <si>
+    <t>058370</t>
+  </si>
+  <si>
+    <t>050320</t>
+  </si>
+  <si>
+    <t>340120</t>
+  </si>
+  <si>
+    <t>332710</t>
+  </si>
+  <si>
+    <t>053110</t>
+  </si>
+  <si>
+    <t>052190</t>
+  </si>
+  <si>
+    <t>046110</t>
+  </si>
+  <si>
+    <t>182690</t>
+  </si>
+  <si>
+    <t>323940</t>
+  </si>
+  <si>
+    <t>225330</t>
+  </si>
+  <si>
+    <t>039670</t>
+  </si>
+  <si>
+    <t>114570</t>
+  </si>
+  <si>
+    <t>066110</t>
+  </si>
+  <si>
+    <t>317320</t>
+  </si>
+  <si>
+    <t>031390</t>
+  </si>
+  <si>
+    <t>033110</t>
+  </si>
+  <si>
+    <t>215750</t>
+  </si>
+  <si>
+    <t>041140</t>
+  </si>
+  <si>
+    <t>323210</t>
+  </si>
+  <si>
+    <t>039230</t>
+  </si>
+  <si>
+    <t>036490</t>
+  </si>
+  <si>
+    <t>221610</t>
+  </si>
+  <si>
+    <t>329560</t>
+  </si>
+  <si>
+    <t>313750</t>
+  </si>
+  <si>
+    <t>317030</t>
+  </si>
+  <si>
+    <t>045890</t>
+  </si>
+  <si>
+    <t>087730</t>
+  </si>
+  <si>
+    <t>033600</t>
+  </si>
+  <si>
+    <t>033430</t>
+  </si>
+  <si>
+    <t>310840</t>
+  </si>
+  <si>
+    <t>178920</t>
+  </si>
+  <si>
+    <t>065620</t>
+  </si>
+  <si>
+    <t>311270</t>
+  </si>
+  <si>
+    <t>141070</t>
+  </si>
+  <si>
+    <t>080440</t>
+  </si>
+  <si>
+    <t>043290</t>
+  </si>
+  <si>
+    <t>028150</t>
+  </si>
+  <si>
+    <t>111820</t>
+  </si>
+  <si>
+    <t>038160</t>
+  </si>
+  <si>
+    <t>086250</t>
+  </si>
+  <si>
+    <t>213090</t>
+  </si>
+  <si>
+    <t>307070</t>
+  </si>
+  <si>
+    <t>307160</t>
+  </si>
+  <si>
+    <t>036260</t>
+  </si>
+  <si>
+    <t>194510</t>
+  </si>
+  <si>
+    <t>277480</t>
+  </si>
+  <si>
+    <t>204990</t>
+  </si>
+  <si>
+    <t>291210</t>
+  </si>
+  <si>
+    <t>095300</t>
+  </si>
+  <si>
+    <t>226350</t>
+  </si>
+  <si>
+    <t>102210</t>
+  </si>
+  <si>
+    <t>900080</t>
+  </si>
+  <si>
+    <t>028040</t>
+  </si>
+  <si>
+    <t>097520</t>
+  </si>
+  <si>
+    <t>195440</t>
+  </si>
+  <si>
+    <t>008800</t>
+  </si>
+  <si>
+    <t>023890</t>
+  </si>
+  <si>
+    <t>073070</t>
+  </si>
+  <si>
+    <t>057500</t>
+  </si>
+  <si>
+    <t>108790</t>
+  </si>
+  <si>
+    <t>134780</t>
+  </si>
+  <si>
+    <t>065940</t>
+  </si>
+  <si>
+    <t>054340</t>
+  </si>
+  <si>
+    <t>197210</t>
+  </si>
+  <si>
+    <t>271740</t>
+  </si>
+  <si>
+    <t>122800</t>
+  </si>
+  <si>
+    <t>077280</t>
+  </si>
+  <si>
+    <t>061460</t>
+  </si>
+  <si>
+    <t>112240</t>
+  </si>
+  <si>
+    <t>123260</t>
+  </si>
+  <si>
+    <t>094190</t>
+  </si>
+  <si>
+    <t>900040</t>
+  </si>
+  <si>
+    <t>281410</t>
+  </si>
+  <si>
+    <t>279410</t>
+  </si>
+  <si>
+    <t>149940</t>
+  </si>
+  <si>
+    <t>030270</t>
+  </si>
+  <si>
+    <t>276920</t>
+  </si>
+  <si>
+    <t>262830</t>
+  </si>
+  <si>
+    <t>257730</t>
+  </si>
+  <si>
+    <t>225650</t>
+  </si>
+  <si>
+    <t>232330</t>
+  </si>
+  <si>
+    <t>026180</t>
+  </si>
+  <si>
+    <t>003670</t>
+  </si>
+  <si>
+    <t>065160</t>
+  </si>
+  <si>
+    <t>192080</t>
+  </si>
+  <si>
+    <t>265480</t>
+  </si>
+  <si>
+    <t>017680</t>
+  </si>
+  <si>
+    <t>035480</t>
+  </si>
+  <si>
+    <t>036420</t>
+  </si>
+  <si>
+    <t>265920</t>
+  </si>
+  <si>
+    <t>264290</t>
+  </si>
+  <si>
+    <t>130960</t>
+  </si>
+  <si>
+    <t>155960</t>
+  </si>
+  <si>
+    <t>123100</t>
+  </si>
+  <si>
+    <t>240540</t>
+  </si>
+  <si>
+    <t>194610</t>
+  </si>
+  <si>
+    <t>026260</t>
+  </si>
+  <si>
+    <t>232270</t>
+  </si>
+  <si>
+    <t>052290</t>
+  </si>
+  <si>
+    <t>208870</t>
+  </si>
+  <si>
+    <t>235010</t>
+  </si>
+  <si>
+    <t>081970</t>
+  </si>
+  <si>
+    <t>900090</t>
+  </si>
+  <si>
+    <t>032040</t>
+  </si>
+  <si>
+    <t>047440</t>
+  </si>
+  <si>
+    <t>016170</t>
+  </si>
+  <si>
+    <t>043580</t>
+  </si>
+  <si>
+    <t>230490</t>
+  </si>
+  <si>
+    <t>099660</t>
+  </si>
+  <si>
+    <t>226850</t>
+  </si>
+  <si>
+    <t>225440</t>
+  </si>
+  <si>
+    <t>900180</t>
+  </si>
+  <si>
+    <t>221200</t>
+  </si>
+  <si>
+    <t>051170</t>
+  </si>
+  <si>
+    <t>222390</t>
+  </si>
+  <si>
+    <t>219860</t>
+  </si>
+  <si>
+    <t>068270</t>
+  </si>
+  <si>
+    <t>024660</t>
+  </si>
+  <si>
+    <t>219580</t>
+  </si>
+  <si>
+    <t>099830</t>
+  </si>
+  <si>
+    <t>223040</t>
+  </si>
+  <si>
+    <t>221950</t>
+  </si>
+  <si>
+    <t>219960</t>
+  </si>
+  <si>
+    <t>087220</t>
+  </si>
+  <si>
+    <t>218710</t>
+  </si>
+  <si>
+    <t>090730</t>
+  </si>
+  <si>
+    <t>039790</t>
+  </si>
+  <si>
+    <t>078780</t>
+  </si>
+  <si>
+    <t>060910</t>
+  </si>
+  <si>
+    <t>025270</t>
+  </si>
+  <si>
+    <t>037340</t>
+  </si>
+  <si>
+    <t>082390</t>
+  </si>
+  <si>
+    <t>158380</t>
+  </si>
+  <si>
+    <t>065270</t>
+  </si>
+  <si>
+    <t>034830</t>
+  </si>
+  <si>
+    <t>111610</t>
+  </si>
+  <si>
+    <t>026960</t>
+  </si>
+  <si>
+    <t>053810</t>
+  </si>
+  <si>
+    <t>068150</t>
+  </si>
+  <si>
+    <t>074150</t>
+  </si>
+  <si>
+    <t>086200</t>
+  </si>
+  <si>
+    <t>066270</t>
+  </si>
+  <si>
+    <t>036220</t>
+  </si>
+  <si>
+    <t>004320</t>
+  </si>
+  <si>
+    <t>101970</t>
+  </si>
+  <si>
+    <t>033630</t>
+  </si>
+  <si>
+    <t>053740</t>
+  </si>
+  <si>
+    <t>053870</t>
+  </si>
+  <si>
+    <t>074130</t>
+  </si>
+  <si>
+    <t>040670</t>
+  </si>
+  <si>
+    <t>065180</t>
+  </si>
+  <si>
+    <t>071930</t>
+  </si>
+  <si>
+    <t>068060</t>
+  </si>
+  <si>
+    <t>053330</t>
+  </si>
+  <si>
+    <t>066350</t>
+  </si>
+  <si>
+    <t>039530</t>
+  </si>
+  <si>
+    <t>090120</t>
+  </si>
+  <si>
+    <t>013450</t>
+  </si>
+  <si>
+    <t>039850</t>
+  </si>
+  <si>
+    <t>032420</t>
+  </si>
+  <si>
+    <t>091690</t>
+  </si>
+  <si>
+    <t>대우스팩2호</t>
+  </si>
+  <si>
+    <t>신양오라컴</t>
+  </si>
+  <si>
+    <t>한화플러스제3호스팩</t>
+  </si>
+  <si>
+    <t>KB제26호스팩</t>
+  </si>
+  <si>
+    <t>유안타제9호스팩</t>
+  </si>
+  <si>
+    <t>하나금융20호스팩</t>
+  </si>
+  <si>
+    <t>상상인제3호스팩</t>
+  </si>
+  <si>
+    <t>유안타제8호스팩</t>
+  </si>
+  <si>
+    <t>삼성머스트스팩5호</t>
+  </si>
+  <si>
+    <t>KB제25호스팩</t>
+  </si>
+  <si>
+    <t>유안타제12호스팩</t>
+  </si>
+  <si>
+    <t>하나머스트7호스팩</t>
+  </si>
+  <si>
+    <t>대신밸런스제13호스팩</t>
+  </si>
+  <si>
+    <t>케이비제23호스팩</t>
+  </si>
+  <si>
+    <t>대신밸런스제18호스팩</t>
+  </si>
+  <si>
+    <t>엔에이치스팩20호</t>
+  </si>
+  <si>
+    <t>미래에셋비전스팩3호</t>
+  </si>
+  <si>
+    <t>IBKS제22호스팩</t>
+  </si>
+  <si>
+    <t>IBKS제19호스팩</t>
+  </si>
+  <si>
+    <t>셀트리온헬스케어</t>
+  </si>
+  <si>
+    <t>IBKS제21호스팩</t>
+  </si>
+  <si>
+    <t>미래에셋드림스팩1호</t>
+  </si>
+  <si>
+    <t>엔에이치스팩28호</t>
+  </si>
+  <si>
+    <t>유안타제13호스팩</t>
+  </si>
+  <si>
+    <t>에이치엠씨제5호스팩</t>
+  </si>
+  <si>
+    <t>우리벤처파트너스</t>
+  </si>
+  <si>
+    <t>케이비제22호스팩</t>
+  </si>
+  <si>
+    <t>엔에이치스팩23호</t>
+  </si>
+  <si>
+    <t>어스앤에어로스페이스</t>
+  </si>
+  <si>
+    <t>미래에셋비전스팩2호</t>
+  </si>
+  <si>
+    <t>디비금융스팩10호</t>
+  </si>
+  <si>
+    <t>DB금융스팩9호</t>
+  </si>
+  <si>
+    <t>케이비제21호스팩</t>
+  </si>
+  <si>
+    <t>비엔케이제1호스팩</t>
+  </si>
+  <si>
+    <t>SBI핀테크솔루션즈</t>
+  </si>
+  <si>
+    <t>하나금융23호스팩</t>
+  </si>
+  <si>
+    <t>엔에이치스팩27호</t>
+  </si>
+  <si>
+    <t>미래에셋비전스팩1호</t>
+  </si>
+  <si>
+    <t>대신밸런스제14호스팩</t>
+  </si>
+  <si>
+    <t>KB제28호스팩</t>
+  </si>
+  <si>
+    <t>SBS콘텐츠허브</t>
+  </si>
+  <si>
+    <t>엔에이치스팩26호</t>
+  </si>
+  <si>
+    <t>하나금융21호스팩</t>
+  </si>
+  <si>
+    <t>한국제11호스팩</t>
+  </si>
+  <si>
+    <t>NICE평가정보</t>
+  </si>
+  <si>
+    <t>한국제10호스팩</t>
+  </si>
+  <si>
+    <t>THE MIDONG</t>
+  </si>
+  <si>
+    <t>IBKS제20호스팩</t>
+  </si>
+  <si>
+    <t>엔에이치스팩25호</t>
+  </si>
+  <si>
+    <t>엔에이치스팩24호</t>
+  </si>
+  <si>
+    <t>하나금융25호스팩</t>
+  </si>
+  <si>
+    <t>DB금융스팩11호</t>
+  </si>
+  <si>
+    <t>IBKS제17호스팩</t>
+  </si>
+  <si>
+    <t>SK증권제8호스팩</t>
+  </si>
+  <si>
+    <t>대신밸런스제15호스팩</t>
+  </si>
+  <si>
+    <t>한화플러스제2호스팩</t>
+  </si>
+  <si>
+    <t>한국제14호스팩</t>
+  </si>
+  <si>
+    <t>유안타제10호스팩</t>
+  </si>
+  <si>
+    <t>하나금융22호스팩</t>
+  </si>
+  <si>
+    <t>신한제10호스팩</t>
+  </si>
+  <si>
+    <t>DB금융스팩8호</t>
+  </si>
+  <si>
+    <t>하나금융24호스팩</t>
+  </si>
+  <si>
+    <t>위니아</t>
+  </si>
+  <si>
+    <t>코엔텍</t>
+  </si>
+  <si>
+    <t>이큐셀</t>
+  </si>
+  <si>
+    <t>애닉</t>
+  </si>
+  <si>
+    <t>MIT</t>
+  </si>
+  <si>
+    <t>이루다</t>
+  </si>
+  <si>
+    <t>SIMPAC Metal</t>
+  </si>
+  <si>
+    <t>파멥신</t>
+  </si>
+  <si>
+    <t>광림</t>
+  </si>
+  <si>
+    <t>비올</t>
+  </si>
+  <si>
+    <t>대유</t>
+  </si>
+  <si>
+    <t>이트론</t>
+  </si>
+  <si>
+    <t>CNH</t>
+  </si>
+  <si>
+    <t>제일바이오</t>
+  </si>
+  <si>
+    <t>교보14호스팩</t>
+  </si>
+  <si>
+    <t>하이제8호스팩</t>
+  </si>
+  <si>
+    <t>에이디칩스</t>
+  </si>
+  <si>
+    <t>퓨처코어</t>
+  </si>
+  <si>
+    <t>인트로메딕</t>
+  </si>
+  <si>
+    <t>푸른소나무</t>
+  </si>
+  <si>
+    <t>장원테크</t>
+  </si>
+  <si>
+    <t>하나29호스팩</t>
+  </si>
+  <si>
+    <t>KH 건설</t>
+  </si>
+  <si>
+    <t>KH 미래물산</t>
+  </si>
+  <si>
+    <t>에스유앤피</t>
+  </si>
+  <si>
+    <t>신영스팩8호</t>
+  </si>
+  <si>
+    <t>하나27호스팩</t>
+  </si>
+  <si>
+    <t>하나28호스팩</t>
+  </si>
+  <si>
+    <t>삼성스팩8호</t>
+  </si>
+  <si>
+    <t>하나26호스팩</t>
+  </si>
+  <si>
+    <t>조광ILI</t>
+  </si>
+  <si>
+    <t>신영스팩9호</t>
+  </si>
+  <si>
+    <t>이화전기</t>
+  </si>
+  <si>
+    <t>웨이포트</t>
+  </si>
+  <si>
+    <t>유진스팩9호</t>
+  </si>
+  <si>
+    <t>제넨바이오</t>
+  </si>
+  <si>
+    <t>삼성스팩7호</t>
+  </si>
+  <si>
+    <t>한송네오텍</t>
+  </si>
+  <si>
+    <t>교보13호스팩</t>
+  </si>
+  <si>
+    <t>엠에프엠코리아</t>
+  </si>
+  <si>
+    <t>삼성스팩9호</t>
+  </si>
+  <si>
+    <t>키움제7호스팩</t>
+  </si>
+  <si>
+    <t>LB루셈</t>
+  </si>
+  <si>
+    <t>한울BnC</t>
+  </si>
+  <si>
+    <t>셀리버리</t>
+  </si>
+  <si>
+    <t>삼성스팩6호</t>
+  </si>
+  <si>
+    <t>비엔씨컴퍼니</t>
+  </si>
+  <si>
+    <t>키움제6호스팩</t>
+  </si>
+  <si>
+    <t>퀀타피아</t>
+  </si>
+  <si>
+    <t>골든센츄리</t>
+  </si>
+  <si>
+    <t>에스엔유</t>
+  </si>
+  <si>
+    <t>비즈니스온</t>
+  </si>
+  <si>
+    <t>한국테크놀로지</t>
+  </si>
+  <si>
+    <t>에스엘에너지</t>
+  </si>
+  <si>
+    <t>교보12호스팩</t>
+  </si>
+  <si>
+    <t>티엘아이</t>
+  </si>
+  <si>
+    <t>제이시스메디칼</t>
+  </si>
+  <si>
+    <t>커넥트웨이브</t>
+  </si>
+  <si>
+    <t>녹원씨엔아이</t>
+  </si>
+  <si>
+    <t>이즈미디어</t>
+  </si>
+  <si>
+    <t>에이티세미콘</t>
+  </si>
+  <si>
+    <t>파나케이아</t>
+  </si>
+  <si>
+    <t>파라다이스</t>
+  </si>
+  <si>
+    <t>유진스팩7호</t>
+  </si>
+  <si>
+    <t>하이제7호스팩</t>
+  </si>
+  <si>
+    <t>스마트솔루션즈</t>
+  </si>
+  <si>
+    <t>대양제지</t>
+  </si>
+  <si>
+    <t>신영스팩7호</t>
+  </si>
+  <si>
+    <t>교보11호스팩</t>
+  </si>
+  <si>
+    <t>신한제9호스팩</t>
+  </si>
+  <si>
+    <t>신한제8호스팩</t>
+  </si>
+  <si>
+    <t>비디아이</t>
+  </si>
+  <si>
+    <t>크루셜텍</t>
+  </si>
+  <si>
+    <t>엘앤에프</t>
+  </si>
+  <si>
+    <t>하이제6호스팩</t>
+  </si>
+  <si>
+    <t>에스에스컴텍</t>
+  </si>
+  <si>
+    <t>디에스앤엘</t>
+  </si>
+  <si>
+    <t>포스코DX</t>
+  </si>
+  <si>
+    <t>유한코스메틱</t>
+  </si>
+  <si>
+    <t>엘아이에스</t>
+  </si>
+  <si>
+    <t>루트로닉</t>
+  </si>
+  <si>
+    <t>유진스팩6호</t>
+  </si>
+  <si>
+    <t>신한제7호스팩</t>
+  </si>
+  <si>
+    <t>삼성스팩4호</t>
+  </si>
+  <si>
+    <t>엔에스브이</t>
+  </si>
+  <si>
+    <t>제이웨이</t>
+  </si>
+  <si>
+    <t>코원플레이</t>
+  </si>
+  <si>
+    <t>오스템임플란트</t>
+  </si>
+  <si>
+    <t>지나인제약</t>
+  </si>
+  <si>
+    <t>엠피씨플러스</t>
+  </si>
+  <si>
+    <t>비에이치</t>
+  </si>
+  <si>
+    <t>SK오션플랜트</t>
+  </si>
+  <si>
+    <t>원익피앤이</t>
+  </si>
+  <si>
+    <t>레드로버</t>
+  </si>
+  <si>
+    <t>신영스팩6호</t>
+  </si>
+  <si>
+    <t>SK5호스팩</t>
+  </si>
+  <si>
+    <t>SK6호스팩</t>
+  </si>
+  <si>
+    <t>코리아센터</t>
+  </si>
+  <si>
+    <t>LX세미콘</t>
+  </si>
+  <si>
+    <t>참존글로벌</t>
+  </si>
+  <si>
+    <t>매직마이크로</t>
+  </si>
+  <si>
+    <t>소리바다</t>
+  </si>
+  <si>
+    <t>에스에이치엔엘</t>
+  </si>
+  <si>
+    <t>하이제5호스팩</t>
+  </si>
+  <si>
+    <t>현진소재</t>
+  </si>
+  <si>
+    <t>스포츠서울</t>
+  </si>
+  <si>
+    <t>맘스터치</t>
+  </si>
+  <si>
+    <t>연이비앤티</t>
+  </si>
+  <si>
+    <t>한일네트웍스</t>
+  </si>
+  <si>
+    <t>에이치엔티</t>
+  </si>
+  <si>
+    <t>세영디앤씨</t>
+  </si>
+  <si>
+    <t>넥슨지티</t>
+  </si>
+  <si>
+    <t>지스마트글로벌</t>
+  </si>
+  <si>
+    <t>자안바이오</t>
+  </si>
+  <si>
+    <t>에이아이비트</t>
+  </si>
+  <si>
+    <t>이엠네트웍스</t>
+  </si>
+  <si>
+    <t>씨엠에스에듀</t>
+  </si>
+  <si>
+    <t>녹십자셀</t>
+  </si>
+  <si>
+    <t>SK머티리얼즈</t>
+  </si>
+  <si>
+    <t>에스제이케이</t>
+  </si>
+  <si>
+    <t>디에스티</t>
+  </si>
+  <si>
+    <t>GS홈쇼핑</t>
+  </si>
+  <si>
+    <t>SK4호스팩</t>
+  </si>
+  <si>
+    <t>한진피앤씨</t>
+  </si>
+  <si>
+    <t>미래테크놀로지</t>
+  </si>
+  <si>
+    <t>PI첨단소재</t>
+  </si>
+  <si>
+    <t>맥스로텍</t>
+  </si>
+  <si>
+    <t>화신테크</t>
+  </si>
+  <si>
+    <t>키움제5호스팩</t>
+  </si>
+  <si>
+    <t>신한제4호스팩</t>
+  </si>
+  <si>
+    <t>아이엠텍</t>
+  </si>
+  <si>
+    <t>코썬바이오</t>
+  </si>
+  <si>
+    <t>바이오빌</t>
+  </si>
+  <si>
+    <t>엠씨넥스</t>
+  </si>
+  <si>
+    <t>에스케이엔펄스</t>
+  </si>
+  <si>
+    <t>이매진아시아</t>
+  </si>
+  <si>
+    <t>에이치디</t>
+  </si>
+  <si>
+    <t>한국제7호스팩</t>
+  </si>
+  <si>
+    <t>미래SCI</t>
+  </si>
+  <si>
+    <t>파티게임즈</t>
+  </si>
+  <si>
+    <t>차이나그레이트</t>
+  </si>
+  <si>
+    <t>에스마크</t>
+  </si>
+  <si>
+    <t>파인넥스</t>
+  </si>
+  <si>
+    <t>한국제5호스팩</t>
+  </si>
+  <si>
+    <t>한컴지엠디</t>
+  </si>
+  <si>
+    <t>인터파크</t>
+  </si>
+  <si>
+    <t>한국제6호스팩</t>
+  </si>
+  <si>
+    <t>이엘케이</t>
+  </si>
+  <si>
+    <t>에스에프씨</t>
+  </si>
+  <si>
+    <t>신한제3호스팩</t>
+  </si>
+  <si>
+    <t>제이테크놀로지</t>
+  </si>
+  <si>
+    <t>SK3호스팩</t>
+  </si>
+  <si>
+    <t>한화수성스팩</t>
+  </si>
+  <si>
+    <t>현대정보기술</t>
+  </si>
+  <si>
+    <t>포스코퓨처엠</t>
+  </si>
+  <si>
+    <t>더블유게임즈</t>
+  </si>
+  <si>
+    <t>에프티이앤이</t>
+  </si>
+  <si>
+    <t>콘텐트리중앙</t>
+  </si>
+  <si>
+    <t>원익테라세미콘</t>
+  </si>
+  <si>
+    <t>SK1호스팩</t>
+  </si>
+  <si>
+    <t>데코앤이</t>
+  </si>
+  <si>
+    <t>한국4호스팩</t>
+  </si>
+  <si>
+    <t>우성아이비</t>
+  </si>
+  <si>
+    <t>트레이스</t>
+  </si>
+  <si>
+    <t>동부제4호스팩</t>
+  </si>
+  <si>
+    <t>차이나하오란</t>
+  </si>
+  <si>
+    <t>카카오M</t>
+  </si>
+  <si>
+    <t>위너지스</t>
+  </si>
+  <si>
+    <t>C&amp;S자산관리</t>
+  </si>
+  <si>
+    <t>에임하이</t>
+  </si>
+  <si>
+    <t>CJ E&amp;M</t>
+  </si>
+  <si>
+    <t>키움스팩4호</t>
+  </si>
+  <si>
+    <t>스틸플라워</t>
+  </si>
+  <si>
+    <t>대우스팩3호</t>
+  </si>
+  <si>
+    <t>유진스팩3호</t>
+  </si>
+  <si>
+    <t>셀트리온</t>
+  </si>
+  <si>
+    <t>교보5호스팩</t>
+  </si>
+  <si>
+    <t>키움스팩3호</t>
+  </si>
+  <si>
+    <t>하림홀딩스</t>
+  </si>
+  <si>
+    <t>아리온</t>
+  </si>
+  <si>
+    <t>연우</t>
+  </si>
+  <si>
+    <t>멜파스</t>
+  </si>
+  <si>
+    <t>케이티비스팩1호</t>
+  </si>
+  <si>
+    <t>한화에이스스팩4호</t>
+  </si>
+  <si>
+    <t>엔에이치스팩7호</t>
+  </si>
+  <si>
+    <t>IBKS제7호스팩</t>
+  </si>
+  <si>
+    <t>이베스트스팩3호</t>
+  </si>
+  <si>
+    <t>하나금융19호스팩</t>
+  </si>
+  <si>
+    <t>미래에셋대우스팩 5호</t>
+  </si>
+  <si>
+    <t>엔에이치스팩22호</t>
+  </si>
+  <si>
+    <t>현대에이블스팩1호</t>
+  </si>
+  <si>
+    <t>대신밸런스제12호스팩</t>
+  </si>
+  <si>
+    <t>미래에셋제3호스팩</t>
+  </si>
+  <si>
+    <t>대신밸런스제10호스팩</t>
+  </si>
+  <si>
+    <t>에이치엠씨제4호스팩</t>
+  </si>
+  <si>
+    <t>대신밸런스제11호스팩</t>
+  </si>
+  <si>
+    <t>하나금융16호스팩</t>
+  </si>
+  <si>
+    <t>IBKS제13호스팩</t>
+  </si>
+  <si>
+    <t>케이비제20호스팩</t>
+  </si>
+  <si>
+    <t>이베스트스팩5호</t>
+  </si>
+  <si>
+    <t>하나금융15호스팩</t>
+  </si>
+  <si>
+    <t>씨그널엔터테인먼트그룹</t>
+  </si>
+  <si>
+    <t>유안타제7호스팩</t>
+  </si>
+  <si>
+    <t>하이에이아이1호스팩</t>
+  </si>
+  <si>
+    <t>케이프이에스제4호</t>
+  </si>
+  <si>
+    <t>케이비제9호스팩</t>
+  </si>
+  <si>
+    <t>하나금융14호스팩</t>
+  </si>
+  <si>
+    <t>골든브릿지제2호스팩</t>
+  </si>
+  <si>
+    <t>케이비드림3호스팩</t>
+  </si>
+  <si>
+    <t>케이비제19호스팩</t>
+  </si>
+  <si>
+    <t>엔에이치SL스팩</t>
+  </si>
+  <si>
+    <t>상상인이안제2호스팩</t>
+  </si>
+  <si>
+    <t>미래에셋대우스팩1호</t>
+  </si>
+  <si>
+    <t>이베스트이안스팩1호</t>
+  </si>
+  <si>
+    <t>케이비제18호스팩</t>
+  </si>
+  <si>
+    <t>케이비제8호스팩</t>
+  </si>
+  <si>
+    <t>한화에스비아이스팩</t>
+  </si>
+  <si>
+    <t>유안타제4호스팩</t>
+  </si>
+  <si>
+    <t>케이비17호스팩</t>
+  </si>
+  <si>
+    <t>한화에이스스팩3호</t>
+  </si>
+  <si>
+    <t>코너스톤네트웍스</t>
+  </si>
+  <si>
+    <t>엔에이치스팩13호</t>
+  </si>
+  <si>
+    <t>한화에이스스팩2호</t>
+  </si>
+  <si>
+    <t>하나머스트3호스팩</t>
+  </si>
+  <si>
+    <t>대신밸런스제4호스팩</t>
+  </si>
+  <si>
+    <t>유안타제2호스팩</t>
+  </si>
+  <si>
+    <t>하나머스트제6호스팩</t>
+  </si>
+  <si>
+    <t>에스앤씨엔진그룹</t>
+  </si>
+  <si>
+    <t>한국아트라스비엑스</t>
+  </si>
+  <si>
+    <t>골든브릿지제3호스팩</t>
+  </si>
+  <si>
+    <t>유네코</t>
+  </si>
+  <si>
+    <t>켐온</t>
+  </si>
+  <si>
+    <t>뉴로스</t>
+  </si>
+  <si>
+    <t>테라셈</t>
+  </si>
+  <si>
+    <t>SNK</t>
+  </si>
+  <si>
+    <t>GV</t>
+  </si>
+  <si>
+    <t>한프</t>
+  </si>
+  <si>
+    <t>럭슬</t>
+  </si>
+  <si>
+    <t>지유온</t>
+  </si>
+  <si>
+    <t>팍스넷</t>
+  </si>
+  <si>
+    <t>케이맥</t>
+  </si>
+  <si>
+    <t>행남사</t>
+  </si>
+  <si>
+    <t>제낙스</t>
+  </si>
+  <si>
+    <t>에이팸</t>
+  </si>
+  <si>
+    <t>퓨전</t>
+  </si>
+  <si>
+    <t>모다</t>
+  </si>
+  <si>
+    <t>화진</t>
+  </si>
+  <si>
+    <t>리드</t>
+  </si>
+  <si>
+    <t>피앤텔</t>
+  </si>
+  <si>
+    <t>썬텍</t>
+  </si>
+  <si>
+    <t>쿠첸</t>
+  </si>
+  <si>
+    <t>신텍</t>
+  </si>
+  <si>
+    <t>썬코어</t>
+  </si>
+  <si>
+    <t>위노바</t>
+  </si>
+  <si>
+    <t>완리</t>
+  </si>
+  <si>
+    <t>아이이</t>
+  </si>
+  <si>
+    <t>프리젠</t>
+  </si>
+  <si>
+    <t>카카오</t>
+  </si>
+  <si>
+    <t>우전</t>
+  </si>
+  <si>
+    <t>지디</t>
+  </si>
+  <si>
+    <t>넥스지</t>
+  </si>
+  <si>
+    <t>레이젠</t>
+  </si>
+  <si>
+    <t>아이디에스</t>
+  </si>
+  <si>
+    <t>한국토지신탁</t>
+  </si>
+  <si>
+    <t>제이앤유글로벌</t>
+  </si>
+  <si>
+    <t>오상헬스케어</t>
+  </si>
+  <si>
+    <t>삼목강업</t>
+  </si>
+  <si>
+    <t>플렉스컴</t>
+  </si>
+  <si>
+    <t>케이엔씨글로벌</t>
+  </si>
+  <si>
+    <t>승화프리텍</t>
+  </si>
+  <si>
+    <t>씨엘인터내셔널</t>
+  </si>
+  <si>
+    <t>엠제이비</t>
+  </si>
+  <si>
+    <t>피엘에이</t>
+  </si>
+  <si>
+    <t>아이팩토리</t>
+  </si>
+  <si>
+    <t>SK컴즈</t>
+  </si>
+  <si>
+    <t>부산방직</t>
+  </si>
+  <si>
+    <t>울트라건설</t>
+  </si>
+  <si>
+    <t>우양에이치씨</t>
+  </si>
+  <si>
+    <t>영진코퍼레이션</t>
+  </si>
+  <si>
+    <t>국제엘렉트릭</t>
+  </si>
+  <si>
+    <t>에이스하이텍</t>
+  </si>
+  <si>
+    <t>씨앤케이인터</t>
+  </si>
+  <si>
+    <t>해피드림</t>
+  </si>
+  <si>
+    <t>티에스엠텍</t>
+  </si>
+  <si>
+    <t>동성하이켐</t>
+  </si>
+  <si>
+    <t>잘만테크</t>
+  </si>
+  <si>
+    <t>디아이디</t>
+  </si>
+  <si>
+    <t>태창파로스</t>
+  </si>
+  <si>
+    <t>SK브로드밴드</t>
+  </si>
+  <si>
+    <t>와이즈파워</t>
+  </si>
+  <si>
+    <t>GT&amp;T</t>
+  </si>
+  <si>
+    <t>디지텍시스템</t>
+  </si>
+  <si>
+    <t>터보테크</t>
+  </si>
+  <si>
+    <t>동서</t>
+  </si>
+  <si>
+    <t>KCW</t>
+  </si>
+  <si>
+    <t>감사의견 거절(계속기업 존속능력 불확실성)</t>
+  </si>
+  <si>
+    <t>기업의 계속성 및 경영의 투명성 등을 종합적을 고려하여 상장폐지기준에 해당한다고 결정</t>
+  </si>
+  <si>
+    <t>제28조제1항제9호에 따라 관리종목 지정 후 공시규정 제19조제1항에 따른 사업보고서 법정제출기한 내 미제출, 최근 2년간 3회 이상 공시규정 제19조제1항의 규정에 의한 사업보고서, 반기보고서 또는 분기보고서 법정제출기한 내 미제출</t>
+  </si>
+  <si>
+    <t>감사의견 거절(내부회계관리제도상의 취약점, 계속기업가정의 불확실성 및 재고자산 관련 감사범위 제한)</t>
+  </si>
+  <si>
+    <t>'14사업연도 자본잠식률 50%이상 사유로 관리종목 지정 후 '15사업연도 반기 감사의견 거절</t>
+  </si>
+  <si>
+    <t>사업보고서, 반기보고서 또는 분기보고서 미제출로 상장규정 제53조제1항제6호에 따라 관리종목으로 지정된 상태에서 공시규정 제19조제1항에 따른 사업보고서, 반기보고서 또는 분기보고서를 법정제출기한내 미제출</t>
+  </si>
+  <si>
+    <t>감사의견 거절(감사범위 제한 및 계속기업 존속능력 불확실성)</t>
+  </si>
+  <si>
+    <t>감사의견거절(범위제한 및 계속기업 존속능력에 대한 불확실성)</t>
+  </si>
+  <si>
+    <t>제28조제1항제9호에 따라 관리종목 지정 후 공시규정 제19조 제1항에 따른 분기보고서 법정기한 내 미제출</t>
+  </si>
+  <si>
+    <t>발행한 어음 또는 수표가 주거래은행에 의하여 최종부도로 결정되거나 거래은행에 의한 거래 정지</t>
+  </si>
+  <si>
+    <t>기업의 계속성 및 경영의 투명성 등을 종합적으로 고려하여 상장폐지기준에 해당한다고 결정</t>
+  </si>
+  <si>
+    <t>발행한 어음 또는 수표가 주거래은행에 의하여 최종부도로 결정되거나 거래은행에 의한 거래정지</t>
+  </si>
+  <si>
+    <t>기업의 계속성 및 경영의 투명성 등을 종합적으로 고려하여 상장폐지 기준에 해당한다고 결정</t>
+  </si>
+  <si>
+    <t>상장예비심사신청서 미제출 등으로 관리종목으로 지정된 날부터 1개월 이내 동 사유 미해소</t>
+  </si>
+  <si>
+    <t>합병상장예비심사신청서 미제출로 관리종목 지정 후 1개월 이내 동 사유 미해소</t>
+  </si>
+  <si>
+    <t>상장예비심사청구서 미제출로 관리종목 지정 후 1개월 이내 동 사유 미해소</t>
+  </si>
+  <si>
+    <t>합병상장예비심사청구서 미제출로 관리종목 지정 후 1개월 이내 동 사유 미해소</t>
+  </si>
+  <si>
+    <t>상장예비심사 청구서 미제출로 관리종목 지정 후 1개월 이내 동 사유 미해소</t>
+  </si>
+  <si>
+    <t>기업의 계속성 및 경영의 투명성 등을 종합적으로 고려하여 상장폐지기준에 해당</t>
+  </si>
+  <si>
+    <t>상장예비심사 청구서 미제출로 관리종목 지정후 1개월 이내 동사유를 미해소</t>
+  </si>
+  <si>
+    <t>상장예비심사 청구서 미제출로 관리종목 지정 후 1개월 이내 동사유 미해소</t>
+  </si>
+  <si>
+    <t>감사의견 거절(감사범위 제한 및 계속기업 존속능력에 대한 불확실성)</t>
+  </si>
+  <si>
+    <t>감사의견 거절(계속기업 존속능력에 대한 불확실성 및 감사범위 제한)</t>
+  </si>
+  <si>
+    <t>감사의견거절(감사범위 제한 및 계속기업 존속능력에 대한 불확실성)</t>
+  </si>
+  <si>
+    <t>최근 2년간 3회 이상 공시규정 제19조제1항의 규정에 의한 사업보고서, 반기보고서 또는 분기보고서 법정제출기한 내 미제출</t>
+  </si>
+  <si>
+    <t>법정제출기한까지 사업보고서를 제출하지 아니한 후, 법정제출기한의 다음날부터 10일이내에 사업보고서를 제출하지 아니함</t>
+  </si>
+  <si>
+    <t>기업의 계속성, 경영의 투명성 또는 그 밖에 코스닥시장의 건전성 등을 종합적으로 고려하여 상장폐지 기준에 해당한다고 결정</t>
+  </si>
+  <si>
+    <t>유가증권시장 상장</t>
+  </si>
+  <si>
+    <t>상장폐지 신청('22.08.31)</t>
+  </si>
+  <si>
+    <t>감사의견 거절(감사범위 제한)</t>
+  </si>
+  <si>
+    <t>감사의견 한정(감사범위 제한)</t>
+  </si>
+  <si>
+    <t>상장폐지 신청('22.04.14)</t>
+  </si>
+  <si>
+    <t>상장폐지신청('15.6.11)</t>
+  </si>
+  <si>
+    <t>상장폐지 신청('24.05.17)</t>
+  </si>
+  <si>
+    <t>상장폐지 신청('25.06.26)</t>
+  </si>
+  <si>
+    <t>상장폐지 신청('17.06.22)</t>
+  </si>
+  <si>
+    <t>상장폐지 신청('15.01.15)</t>
+  </si>
+  <si>
+    <t>상장폐지 신청('23.06.28)</t>
+  </si>
+  <si>
+    <t>상장폐지 신청('25.11.06)</t>
+  </si>
+  <si>
+    <t>상장폐지 신청('22.03.30)</t>
+  </si>
+  <si>
+    <t>상장폐지신청('17.02.07)</t>
+  </si>
+  <si>
+    <t>최근 5사업연도 연속 영업손실 발생</t>
+  </si>
+  <si>
+    <t>감사범위제한으로 인한 한정의견</t>
+  </si>
+  <si>
+    <t>2반기 연속 자본잠식률 50% 이상</t>
+  </si>
+  <si>
+    <t>타법인의 완전자회사로 편입</t>
+  </si>
+  <si>
+    <t>피흡수합병(스팩소멸합병)</t>
+  </si>
+  <si>
+    <t>해산사유 발생(파산선고)</t>
+  </si>
+  <si>
+    <t>상장예비심사청구서 미제출</t>
+  </si>
+  <si>
+    <t>감사의견거절(감사범위 제한)</t>
+  </si>
+  <si>
+    <t>감사의견거절(감사범위제한)</t>
+  </si>
+  <si>
+    <t>피흡수합병</t>
+  </si>
+  <si>
+    <t>감사범위 제한</t>
+  </si>
+  <si>
+    <t>감사의견 거절</t>
+  </si>
+  <si>
+    <t>감사의견 거절(감사범위 제한 및 계속기업가정 불확실성)</t>
+  </si>
+  <si>
+    <t>감사의견 거절(감사범위 제한 및 계속기업 가정 불확실성)</t>
+  </si>
+  <si>
+    <t>감사의견 거절(감사범위 제한 및 기업회계기준 위배)</t>
+  </si>
+  <si>
+    <t>감사의견거절(감사범위제한 및 계속기업 존속 불확실)</t>
+  </si>
+  <si>
+    <t>'16사업연도 감사의견거절(계속기업 존속능력에 대한 불확실성) 및 '17사업연도 반기 감사의견거절(계속기업 존속능력에 대한 불확실성)</t>
+  </si>
+  <si>
+    <t>자본전액잠식 등</t>
+  </si>
+  <si>
+    <t>감사의견 거절(감사범위 제한으로 인한 의견거절)</t>
+  </si>
+  <si>
+    <t>자본전액잠식</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,6 +2399,12 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -83,7 +2414,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -91,19 +2422,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준_Sheet1" xfId="1" xr:uid="{0B0EB4F9-756A-41F9-9644-BB34E45F4F88}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -435,8 +2794,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD877FFF-C6B5-47F9-9910-EE30E2676E92}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D358"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="3" width="41.5" customWidth="1"/>
+    <col min="4" max="4" width="71.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -450,6 +2813,5004 @@
       </c>
       <c r="D1" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2" s="3">
+        <v>46076</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C3" s="3">
+        <v>46063</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C4" s="3">
+        <v>46057</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C5" s="3">
+        <v>46051</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46050</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46050</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C8" s="3">
+        <v>46049</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C9" s="3">
+        <v>46048</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C10" s="3">
+        <v>46044</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C11" s="3">
+        <v>46036</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C12" s="3">
+        <v>46036</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46036</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C14" s="3">
+        <v>46036</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C15" s="3">
+        <v>46036</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="70" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C16" s="3">
+        <v>46021</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C17" s="3">
+        <v>46020</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C18" s="3">
+        <v>46001</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C19" s="3">
+        <v>45987</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C20" s="3">
+        <v>45987</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C21" s="3">
+        <v>45978</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C22" s="3">
+        <v>45974</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C23" s="3">
+        <v>45957</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C24" s="3">
+        <v>45953</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C25" s="3">
+        <v>45946</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C26" s="3">
+        <v>45944</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C27" s="3">
+        <v>45940</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C28" s="3">
+        <v>45910</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C29" s="3">
+        <v>45910</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C30" s="3">
+        <v>45909</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C31" s="3">
+        <v>45908</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C32" s="3">
+        <v>45891</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C33" s="3">
+        <v>45890</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C34" s="3">
+        <v>45890</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C35" s="3">
+        <v>45870</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C36" s="3">
+        <v>45866</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C37" s="3">
+        <v>45862</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C38" s="3">
+        <v>45859</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C39" s="3">
+        <v>45852</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C40" s="3">
+        <v>45849</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C41" s="3">
+        <v>45849</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C42" s="3">
+        <v>45847</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C43" s="3">
+        <v>45847</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C44" s="3">
+        <v>45846</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C45" s="3">
+        <v>45827</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C46" s="3">
+        <v>45827</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="84" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C47" s="3">
+        <v>45826</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="84" x14ac:dyDescent="0.45">
+      <c r="A48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C48" s="3">
+        <v>45826</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C49" s="3">
+        <v>45825</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A50" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C50" s="3">
+        <v>45824</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A51" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C51" s="3">
+        <v>45819</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A52" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C52" s="3">
+        <v>45810</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C53" s="3">
+        <v>45810</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C54" s="3">
+        <v>45803</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A55" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C55" s="3">
+        <v>45803</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A56" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C56" s="3">
+        <v>45793</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A57" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C57" s="3">
+        <v>45793</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A58" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C58" s="3">
+        <v>45792</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C59" s="3">
+        <v>45791</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C60" s="3">
+        <v>45776</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A61" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C61" s="3">
+        <v>45751</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="84" x14ac:dyDescent="0.45">
+      <c r="A62" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C62" s="3">
+        <v>45747</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A63" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C63" s="3">
+        <v>45744</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A64" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C64" s="3">
+        <v>45744</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A65" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C65" s="3">
+        <v>45733</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="84" x14ac:dyDescent="0.45">
+      <c r="A66" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C66" s="3">
+        <v>45723</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A67" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C67" s="3">
+        <v>45723</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C68" s="3">
+        <v>45716</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C69" s="3">
+        <v>45709</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A70" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C70" s="3">
+        <v>45707</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A71" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C71" s="3">
+        <v>45702</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A72" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C72" s="3">
+        <v>45702</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A73" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C73" s="3">
+        <v>45699</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A74" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C74" s="3">
+        <v>45698</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A75" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C75" s="3">
+        <v>45692</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A76" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C76" s="3">
+        <v>45678</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="336" x14ac:dyDescent="0.45">
+      <c r="A77" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C77" s="3">
+        <v>45665</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A78" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C78" s="3">
+        <v>45652</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A79" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C79" s="3">
+        <v>45649</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A80" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C80" s="3">
+        <v>45646</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A81" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C81" s="3">
+        <v>45645</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A82" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C82" s="3">
+        <v>45639</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A83" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C83" s="3">
+        <v>45630</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A84" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C84" s="3">
+        <v>45618</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A85" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C85" s="3">
+        <v>45616</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A86" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C86" s="3">
+        <v>45615</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A87" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C87" s="3">
+        <v>45610</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A88" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C88" s="3">
+        <v>45603</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A89" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C89" s="3">
+        <v>45602</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A90" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C90" s="3">
+        <v>45587</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A91" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C91" s="3">
+        <v>45572</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A92" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C92" s="3">
+        <v>45562</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A93" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C93" s="3">
+        <v>45559</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A94" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C94" s="3">
+        <v>45541</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A95" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C95" s="3">
+        <v>45538</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A96" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C96" s="3">
+        <v>45502</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A97" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C97" s="3">
+        <v>45499</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A98" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C98" s="3">
+        <v>45498</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A99" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C99" s="3">
+        <v>45483</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A100" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C100" s="3">
+        <v>45475</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A101" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C101" s="3">
+        <v>45468</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A102" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C102" s="3">
+        <v>45467</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A103" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C103" s="3">
+        <v>45464</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A104" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C104" s="3">
+        <v>45460</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A105" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C105" s="3">
+        <v>45460</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A106" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C106" s="3">
+        <v>45454</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A107" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C107" s="3">
+        <v>45450</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A108" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C108" s="3">
+        <v>45426</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A109" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="C109" s="3">
+        <v>45415</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A110" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C110" s="3">
+        <v>45415</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A111" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C111" s="3">
+        <v>45412</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A112" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C112" s="3">
+        <v>45407</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A113" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C113" s="3">
+        <v>45376</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A114" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C114" s="3">
+        <v>45357</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A115" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C115" s="3">
+        <v>45341</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A116" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C116" s="3">
+        <v>45337</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A117" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C117" s="3">
+        <v>45337</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A118" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C118" s="3">
+        <v>45323</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A119" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C119" s="3">
+        <v>45320</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A120" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C120" s="3">
+        <v>45316</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A121" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C121" s="3">
+        <v>45314</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A122" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C122" s="3">
+        <v>45303</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A123" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C123" s="3">
+        <v>45295</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A124" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C124" s="3">
+        <v>45294</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A125" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C125" s="3">
+        <v>45293</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A126" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C126" s="3">
+        <v>45287</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A127" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C127" s="3">
+        <v>45281</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A128" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C128" s="3">
+        <v>45278</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A129" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C129" s="3">
+        <v>45273</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A130" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C130" s="3">
+        <v>45266</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A131" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C131" s="3">
+        <v>45254</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A132" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C132" s="3">
+        <v>45233</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A133" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C133" s="3">
+        <v>45233</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A134" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C134" s="3">
+        <v>45226</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A135" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C135" s="3">
+        <v>45219</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A136" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C136" s="3">
+        <v>45191</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A137" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C137" s="3">
+        <v>45188</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A138" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C138" s="3">
+        <v>45187</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A139" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C139" s="3">
+        <v>45177</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A140" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C140" s="3">
+        <v>45169</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A141" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C141" s="3">
+        <v>45166</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A142" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C142" s="3">
+        <v>45152</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A143" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C143" s="3">
+        <v>45146</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="84" x14ac:dyDescent="0.45">
+      <c r="A144" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C144" s="3">
+        <v>45128</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A145" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C145" s="3">
+        <v>45124</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A146" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C146" s="3">
+        <v>45124</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A147" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C147" s="3">
+        <v>45097</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A148" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C148" s="3">
+        <v>45069</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A149" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="C149" s="3">
+        <v>45063</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A150" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C150" s="3">
+        <v>45054</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A151" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C151" s="3">
+        <v>45044</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A152" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C152" s="3">
+        <v>45036</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A153" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C153" s="3">
+        <v>45035</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="84" x14ac:dyDescent="0.45">
+      <c r="A154" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C154" s="3">
+        <v>45030</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="84" x14ac:dyDescent="0.45">
+      <c r="A155" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C155" s="3">
+        <v>45015</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A156" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C156" s="3">
+        <v>45001</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A157" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C157" s="3">
+        <v>44995</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A158" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="C158" s="3">
+        <v>44994</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A159" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C159" s="3">
+        <v>44987</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A160" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C160" s="3">
+        <v>44978</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A161" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C161" s="3">
+        <v>44974</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A162" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="C162" s="3">
+        <v>44943</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A163" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C163" s="3">
+        <v>44924</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A164" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C164" s="3">
+        <v>44921</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A165" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="C165" s="3">
+        <v>44918</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A166" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="C166" s="3">
+        <v>44911</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A167" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C167" s="3">
+        <v>44911</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A168" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="C168" s="3">
+        <v>44903</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A169" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C169" s="3">
+        <v>44894</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A170" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C170" s="3">
+        <v>44874</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A171" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C171" s="3">
+        <v>44869</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A172" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C172" s="3">
+        <v>44868</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A173" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C173" s="3">
+        <v>44865</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A174" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="C174" s="3">
+        <v>44860</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A175" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C175" s="3">
+        <v>44852</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A176" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C176" s="3">
+        <v>44852</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A177" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C177" s="3">
+        <v>44851</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A178" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="C178" s="3">
+        <v>44851</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A179" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C179" s="3">
+        <v>44839</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A180" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="C180" s="3">
+        <v>44830</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A181" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C181" s="3">
+        <v>44826</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A182" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C182" s="3">
+        <v>44811</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A183" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C183" s="3">
+        <v>44770</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A184" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C184" s="3">
+        <v>44739</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A185" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C185" s="3">
+        <v>44712</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A186" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C186" s="3">
+        <v>44712</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A187" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C187" s="3">
+        <v>44708</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A188" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="C188" s="3">
+        <v>44699</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A189" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C189" s="3">
+        <v>44690</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A190" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C190" s="3">
+        <v>44677</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A191" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C191" s="3">
+        <v>44671</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A192" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C192" s="3">
+        <v>44666</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A193" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="C193" s="3">
+        <v>44657</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A194" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C194" s="3">
+        <v>44655</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A195" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C195" s="3">
+        <v>44637</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A196" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C196" s="3">
+        <v>44615</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A197" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C197" s="3">
+        <v>44609</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A198" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C198" s="3">
+        <v>44596</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="154" x14ac:dyDescent="0.45">
+      <c r="A199" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C199" s="3">
+        <v>44566</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A200" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C200" s="3">
+        <v>44557</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A201" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="C201" s="3">
+        <v>44550</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A202" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C202" s="3">
+        <v>44537</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A203" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="C203" s="3">
+        <v>44537</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A204" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C204" s="3">
+        <v>44517</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A205" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="C205" s="3">
+        <v>44504</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A206" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C206" s="3">
+        <v>44477</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A207" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="C207" s="3">
+        <v>44477</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A208" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C208" s="3">
+        <v>44475</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A209" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C209" s="3">
+        <v>44474</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A210" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C210" s="3">
+        <v>44469</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A211" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C211" s="3">
+        <v>44462</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="154" x14ac:dyDescent="0.45">
+      <c r="A212" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C212" s="3">
+        <v>44455</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A213" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C213" s="3">
+        <v>44452</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A214" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="C214" s="3">
+        <v>44441</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A215" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C215" s="3">
+        <v>44439</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A216" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="C216" s="3">
+        <v>44431</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A217" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="C217" s="3">
+        <v>44419</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A218" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C218" s="3">
+        <v>44417</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A219" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C219" s="3">
+        <v>44417</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A220" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C220" s="3">
+        <v>44410</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A221" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="C221" s="3">
+        <v>44397</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A222" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C222" s="3">
+        <v>44393</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A223" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C223" s="3">
+        <v>44390</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A224" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="C224" s="3">
+        <v>44385</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A225" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C225" s="3">
+        <v>44383</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="196" x14ac:dyDescent="0.45">
+      <c r="A226" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C226" s="3">
+        <v>44361</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A227" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C227" s="3">
+        <v>44358</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A228" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="C228" s="3">
+        <v>44357</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A229" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="C229" s="3">
+        <v>44354</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A230" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C230" s="3">
+        <v>44351</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A231" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C231" s="3">
+        <v>44305</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A232" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="C232" s="3">
+        <v>44305</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="196" x14ac:dyDescent="0.45">
+      <c r="A233" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C233" s="3">
+        <v>44299</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A234" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C234" s="3">
+        <v>44242</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A235" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C235" s="3">
+        <v>44211</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A236" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C236" s="3">
+        <v>44188</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A237" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C237" s="3">
+        <v>44083</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A238" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C238" s="3">
+        <v>44063</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A239" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="C239" s="3">
+        <v>44054</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A240" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C240" s="3">
+        <v>44043</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A241" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C241" s="3">
+        <v>44039</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A242" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C242" s="3">
+        <v>44028</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A243" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C243" s="3">
+        <v>44022</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A244" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C244" s="3">
+        <v>44015</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A245" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="C245" s="3">
+        <v>44014</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A246" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C246" s="3">
+        <v>44012</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A247" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C247" s="3">
+        <v>44000</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A248" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C248" s="3">
+        <v>43973</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" ht="196" x14ac:dyDescent="0.45">
+      <c r="A249" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C249" s="3">
+        <v>43973</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A250" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="C250" s="3">
+        <v>43972</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" ht="84" x14ac:dyDescent="0.45">
+      <c r="A251" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C251" s="3">
+        <v>43972</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A252" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="C252" s="3">
+        <v>43965</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" ht="364" x14ac:dyDescent="0.45">
+      <c r="A253" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C253" s="3">
+        <v>43931</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A254" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C254" s="3">
+        <v>43893</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A255" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="C255" s="3">
+        <v>43873</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A256" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C256" s="3">
+        <v>43846</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A257" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C257" s="3">
+        <v>43845</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A258" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C258" s="3">
+        <v>43833</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A259" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C259" s="3">
+        <v>43811</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A260" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C260" s="3">
+        <v>43805</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" ht="154" x14ac:dyDescent="0.45">
+      <c r="A261" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C261" s="3">
+        <v>43789</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A262" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C262" s="3">
+        <v>43756</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A263" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="C263" s="3">
+        <v>43748</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A264" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C264" s="3">
+        <v>43739</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A265" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C265" s="3">
+        <v>43724</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A266" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C266" s="3">
+        <v>43707</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A267" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C267" s="3">
+        <v>43663</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A268" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="C268" s="3">
+        <v>43614</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A269" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C269" s="3">
+        <v>43588</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A270" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C270" s="3">
+        <v>43536</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A271" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C271" s="3">
+        <v>43516</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A272" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C272" s="3">
+        <v>43494</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" ht="168" x14ac:dyDescent="0.45">
+      <c r="A273" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="C273" s="3">
+        <v>43467</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A274" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="C274" s="3">
+        <v>43385</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A275" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C275" s="3">
+        <v>43385</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A276" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C276" s="3">
+        <v>43385</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A277" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C277" s="3">
+        <v>43385</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A278" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="C278" s="3">
+        <v>43384</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A279" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="C279" s="3">
+        <v>43384</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A280" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="C280" s="3">
+        <v>43384</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A281" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C281" s="3">
+        <v>43384</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A282" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="C282" s="3">
+        <v>43384</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A283" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="C283" s="3">
+        <v>43361</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A284" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="C284" s="3">
+        <v>43322</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A285" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C285" s="3">
+        <v>43307</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A286" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C286" s="3">
+        <v>43299</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A287" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C287" s="3">
+        <v>43298</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A288" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C288" s="3">
+        <v>43297</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" ht="154" x14ac:dyDescent="0.45">
+      <c r="A289" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C289" s="3">
+        <v>43290</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A290" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="C290" s="3">
+        <v>43256</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A291" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C291" s="3">
+        <v>43248</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A292" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C292" s="3">
+        <v>43243</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A293" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C293" s="3">
+        <v>43228</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A294" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C294" s="3">
+        <v>43224</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A295" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C295" s="3">
+        <v>43207</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A296" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C296" s="3">
+        <v>43189</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A297" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C297" s="3">
+        <v>43189</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" ht="210" x14ac:dyDescent="0.45">
+      <c r="A298" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C298" s="3">
+        <v>43174</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A299" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="C299" s="3">
+        <v>43172</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A300" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="C300" s="3">
+        <v>43168</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A301" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C301" s="3">
+        <v>43161</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A302" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C302" s="3">
+        <v>43154</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A303" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C303" s="3">
+        <v>43145</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A304" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="C304" s="3">
+        <v>43140</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A305" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C305" s="3">
+        <v>43138</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A306" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C306" s="3">
+        <v>43119</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A307" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C307" s="3">
+        <v>43104</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A308" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C308" s="3">
+        <v>43095</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A309" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C309" s="3">
+        <v>43089</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A310" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C310" s="3">
+        <v>43045</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A311" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C311" s="3">
+        <v>43028</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A312" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C312" s="3">
+        <v>43024</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A313" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C313" s="3">
+        <v>43007</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" ht="168" x14ac:dyDescent="0.45">
+      <c r="A314" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C314" s="3">
+        <v>42990</v>
+      </c>
+      <c r="D314" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A315" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C315" s="3">
+        <v>42947</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A316" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C316" s="3">
+        <v>42941</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A317" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="C317" s="3">
+        <v>42926</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A318" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C318" s="3">
+        <v>42923</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A319" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C319" s="3">
+        <v>42901</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" ht="126" x14ac:dyDescent="0.45">
+      <c r="A320" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C320" s="3">
+        <v>42884</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A321" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C321" s="3">
+        <v>42866</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A322" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C322" s="3">
+        <v>42863</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A323" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C323" s="3">
+        <v>42863</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A324" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="C324" s="3">
+        <v>42838</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A325" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="C325" s="3">
+        <v>42801</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A326" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="C326" s="3">
+        <v>42793</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A327" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="C327" s="3">
+        <v>42790</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" ht="84" x14ac:dyDescent="0.45">
+      <c r="A328" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C328" s="3">
+        <v>42632</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A329" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C329" s="3">
+        <v>42621</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A330" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="C330" s="3">
+        <v>42618</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A331" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="C331" s="3">
+        <v>42600</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A332" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="C332" s="3">
+        <v>42576</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A333" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="C333" s="3">
+        <v>42566</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A334" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="C334" s="3">
+        <v>42562</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A335" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="C335" s="3">
+        <v>42499</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" ht="70" x14ac:dyDescent="0.45">
+      <c r="A336" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C336" s="3">
+        <v>42499</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A337" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="C337" s="3">
+        <v>42488</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A338" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="C338" s="3">
+        <v>42481</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A339" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="C339" s="3">
+        <v>42472</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" ht="196" x14ac:dyDescent="0.45">
+      <c r="A340" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C340" s="3">
+        <v>42394</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A341" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="C341" s="3">
+        <v>42292</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" ht="196" x14ac:dyDescent="0.45">
+      <c r="A342" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="C342" s="3">
+        <v>42265</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" ht="196" x14ac:dyDescent="0.45">
+      <c r="A343" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C343" s="3">
+        <v>42208</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A344" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="C344" s="3">
+        <v>42205</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A345" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C345" s="3">
+        <v>42201</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A346" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="C346" s="3">
+        <v>42195</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A347" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="C347" s="3">
+        <v>42186</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" ht="154" x14ac:dyDescent="0.45">
+      <c r="A348" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="C348" s="3">
+        <v>42144</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A349" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C349" s="3">
+        <v>42143</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A350" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="C350" s="3">
+        <v>42143</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" ht="112" x14ac:dyDescent="0.45">
+      <c r="A351" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C351" s="3">
+        <v>42137</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" ht="56" x14ac:dyDescent="0.45">
+      <c r="A352" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="C352" s="3">
+        <v>42128</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A353" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C353" s="3">
+        <v>42117</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" ht="28" x14ac:dyDescent="0.45">
+      <c r="A354" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="C354" s="3">
+        <v>42107</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" ht="154" x14ac:dyDescent="0.45">
+      <c r="A355" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="C355" s="3">
+        <v>42080</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" ht="42" x14ac:dyDescent="0.45">
+      <c r="A356" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="C356" s="3">
+        <v>42045</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" ht="140" x14ac:dyDescent="0.45">
+      <c r="A357" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="C357" s="3">
+        <v>42031</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" ht="98" x14ac:dyDescent="0.45">
+      <c r="A358" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C358" s="3">
+        <v>42025</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>739</v>
       </c>
     </row>
   </sheetData>
